--- a/backend/uploads/file.xlsx
+++ b/backend/uploads/file.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dell\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coding\nodeprojects\proto\backend\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D01C42E0-F27A-43B5-8E3E-D581D725B3E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{063159E0-8071-4A3D-8902-5FF52B30EBE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{A1B389CC-E8F0-4DD9-9EE3-A97C3C9E5A94}"/>
   </bookViews>
@@ -25,18 +25,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>url</t>
   </si>
   <si>
-    <t>https://stackoverflow.com</t>
-  </si>
-  <si>
     <t>https://www.wikipedia.org</t>
   </si>
   <si>
     <t>https://en.wikipedia.org/wiki/Sachin_Tendulkar</t>
+  </si>
+  <si>
+    <t>https://example.com</t>
+  </si>
+  <si>
+    <t>https://httpbin.org</t>
+  </si>
+  <si>
+    <t>https://www.iana.org/domains/reserved</t>
   </si>
 </sst>
 </file>
@@ -413,10 +419,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CD273FC-75E2-41C8-A9C3-365695CE7FFE}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="23.7265625" customWidth="1"/>
+    <col min="1" max="1" width="44.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -426,28 +432,39 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" s="1"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>1</v>
-      </c>
       <c r="B4" s="2"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>4</v>
+      </c>
       <c r="B5" s="2"/>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{FA48B622-34AD-40F7-9B47-90F412967B29}"/>
     <hyperlink ref="A3" r:id="rId2" xr:uid="{B1D9B04B-5CE2-460A-A8EF-C6634F9848F8}"/>
+    <hyperlink ref="A4" r:id="rId3" xr:uid="{6DC1940D-BFD6-41D0-8CCD-B1EF0837C255}"/>
+    <hyperlink ref="A5" r:id="rId4" xr:uid="{B2240C58-5A8D-4191-A887-E22EEA4C694E}"/>
+    <hyperlink ref="A6" r:id="rId5" xr:uid="{66D5FD5A-5FF8-4F6E-8D50-F3C564C62289}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/backend/uploads/file.xlsx
+++ b/backend/uploads/file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coding\nodeprojects\proto\backend\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{063159E0-8071-4A3D-8902-5FF52B30EBE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D3AB63D-703B-490B-808F-CA9DB45C4C39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{A1B389CC-E8F0-4DD9-9EE3-A97C3C9E5A94}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>url</t>
   </si>
@@ -36,13 +36,10 @@
     <t>https://en.wikipedia.org/wiki/Sachin_Tendulkar</t>
   </si>
   <si>
-    <t>https://example.com</t>
-  </si>
-  <si>
     <t>https://httpbin.org</t>
   </si>
   <si>
-    <t>https://www.iana.org/domains/reserved</t>
+    <t>https://en.wikipedia.org/wiki/Artificial_intelligence</t>
   </si>
 </sst>
 </file>
@@ -419,7 +416,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CD273FC-75E2-41C8-A9C3-365695CE7FFE}">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="44.08984375" customWidth="1"/>
@@ -443,20 +440,15 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" s="2"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="2"/>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
-        <v>5</v>
-      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -464,7 +456,6 @@
     <hyperlink ref="A3" r:id="rId2" xr:uid="{B1D9B04B-5CE2-460A-A8EF-C6634F9848F8}"/>
     <hyperlink ref="A4" r:id="rId3" xr:uid="{6DC1940D-BFD6-41D0-8CCD-B1EF0837C255}"/>
     <hyperlink ref="A5" r:id="rId4" xr:uid="{B2240C58-5A8D-4191-A887-E22EEA4C694E}"/>
-    <hyperlink ref="A6" r:id="rId5" xr:uid="{66D5FD5A-5FF8-4F6E-8D50-F3C564C62289}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
